--- a/docs/Units Details.xlsx
+++ b/docs/Units Details.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet name="Infantry" sheetId="1" r:id="rId1"/>
     <sheet name="Vehicles" sheetId="2" r:id="rId2"/>
+    <sheet name="Aircraft" sheetId="3" r:id="rId3"/>
+    <sheet name="Hardpoint Weapons" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="97">
   <si>
     <t>Infantry</t>
   </si>
@@ -129,43 +131,196 @@
     <t>Vehicles</t>
   </si>
   <si>
+    <t>Hardpoints (S/M/L/H)</t>
+  </si>
+  <si>
+    <t>Armour Options</t>
+  </si>
+  <si>
+    <t>V-12L Raptor APC</t>
+  </si>
+  <si>
+    <t>1/0/0/0</t>
+  </si>
+  <si>
+    <t>V-12 Rex APC</t>
+  </si>
+  <si>
+    <t>1/1/0/0</t>
+  </si>
+  <si>
+    <t>Uparmour</t>
+  </si>
+  <si>
+    <t>V-15 Seahorse APC</t>
+  </si>
+  <si>
+    <t>V-16 Armadillo APC</t>
+  </si>
+  <si>
+    <t>1/1/1/0</t>
+  </si>
+  <si>
+    <t>M-22 MCV</t>
+  </si>
+  <si>
+    <t>(1/1/0/0) OR (0/0/0/1)</t>
+  </si>
+  <si>
+    <t>M-22L MCV</t>
+  </si>
+  <si>
+    <t>M-54 IFV</t>
+  </si>
+  <si>
+    <t>M-54S ISV</t>
+  </si>
+  <si>
+    <t>(0/1/1/0) OR (0/0/0/1)</t>
+  </si>
+  <si>
+    <t>KF101 MBT</t>
+  </si>
+  <si>
+    <t>Tiger 3A5</t>
+  </si>
+  <si>
+    <t>1/0/1/0</t>
+  </si>
+  <si>
+    <t>Fighter M16</t>
+  </si>
+  <si>
+    <t>2/0/1/0</t>
+  </si>
+  <si>
+    <t>Pickup Truck</t>
+  </si>
+  <si>
+    <t>(1/0/0/0) OR (0/1/0/0)</t>
+  </si>
+  <si>
+    <t>Uparmour, Drone Cage</t>
+  </si>
+  <si>
+    <t>T-90</t>
+  </si>
+  <si>
+    <t>ERA, Drone Cage</t>
+  </si>
+  <si>
+    <t>T-72M</t>
+  </si>
+  <si>
+    <t>T-14</t>
+  </si>
+  <si>
+    <t>Van</t>
+  </si>
+  <si>
     <t>Weapon Options</t>
   </si>
   <si>
-    <t>V-12L Raptor APC</t>
-  </si>
-  <si>
-    <t>V-12 Rex APC</t>
-  </si>
-  <si>
-    <t>V-15 Seahorse APC</t>
-  </si>
-  <si>
-    <t>V-16 Armadillo APC</t>
-  </si>
-  <si>
-    <t>M-22 MCV</t>
-  </si>
-  <si>
-    <t>M-22L MCV</t>
-  </si>
-  <si>
-    <t>M-54 IFV</t>
-  </si>
-  <si>
-    <t>M-54S ISV</t>
-  </si>
-  <si>
-    <t>KF101 MBT</t>
-  </si>
-  <si>
-    <t>Tiger 3A5</t>
-  </si>
-  <si>
-    <t>Fighter M16</t>
-  </si>
-  <si>
-    <t>Pickup Truck</t>
+    <t>F-177 Hawk CAS</t>
+  </si>
+  <si>
+    <t>C-700 Ostritch SSTO</t>
+  </si>
+  <si>
+    <t>S-520 Emu</t>
+  </si>
+  <si>
+    <t>S-550 Fighting Emu</t>
+  </si>
+  <si>
+    <t>F-77 Fighter</t>
+  </si>
+  <si>
+    <t>F-76 ASF</t>
+  </si>
+  <si>
+    <t>F-92 Interceptor</t>
+  </si>
+  <si>
+    <t>F-69 Multirole</t>
+  </si>
+  <si>
+    <t>B-8 Bomber</t>
+  </si>
+  <si>
+    <t>B-72 Stratofortress</t>
+  </si>
+  <si>
+    <t>B-705 CAS</t>
+  </si>
+  <si>
+    <t>B-720 AWACS</t>
+  </si>
+  <si>
+    <t>Weapon</t>
+  </si>
+  <si>
+    <t>Hardpoint Type (S/M/L/H)</t>
+  </si>
+  <si>
+    <t>MMG</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>50. Cal MG</t>
+  </si>
+  <si>
+    <t>Grenade Launcher</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>Autocannon</t>
+  </si>
+  <si>
+    <t>Dual ATGM Launcher</t>
+  </si>
+  <si>
+    <t>Dual AA Missile Launcher</t>
+  </si>
+  <si>
+    <t>AA Shorad Gun</t>
+  </si>
+  <si>
+    <t>Small Ground Radar</t>
+  </si>
+  <si>
+    <t>120mm Gun</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>130mm Railgun</t>
+  </si>
+  <si>
+    <t>x8 ATGM Launcher</t>
+  </si>
+  <si>
+    <t>AA Missile Launcher</t>
+  </si>
+  <si>
+    <t>Air Defense Radar</t>
+  </si>
+  <si>
+    <t>ATGM Autolauncher</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>Large AA Missile Launcher</t>
+  </si>
+  <si>
+    <t>Air Defense Radar Array</t>
   </si>
 </sst>
 </file>
@@ -178,14 +333,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -641,148 +789,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1299,12 +1447,241 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="18.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="11.6666666666667" customWidth="1"/>
+    <col min="3" max="3" width="32.5555555555556" customWidth="1"/>
+    <col min="4" max="4" width="20.8888888888889" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="18.7777777777778" customWidth="1"/>
-    <col min="2" max="2" width="11.6666666666667" customWidth="1"/>
-    <col min="3" max="3" width="16.7777777777778" customWidth="1"/>
+    <col min="1" max="1" width="20.8888888888889" customWidth="1"/>
+    <col min="2" max="2" width="15.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="18.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1315,12 +1692,12 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
@@ -1328,7 +1705,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
@@ -1336,7 +1713,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
@@ -1344,7 +1721,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
@@ -1352,7 +1729,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
@@ -1360,7 +1737,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
@@ -1368,7 +1745,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
@@ -1376,7 +1753,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="B9" t="s">
         <v>6</v>
@@ -1384,7 +1761,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="B10" t="s">
         <v>6</v>
@@ -1392,7 +1769,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="B11" t="s">
         <v>6</v>
@@ -1400,7 +1777,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="B12" t="s">
         <v>6</v>
@@ -1408,10 +1785,162 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="23.4444444444444" customWidth="1"/>
+    <col min="2" max="2" width="23.5555555555556" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
